--- a/ig/nr-add-marital-status-binding/ValueSet-fr-core-vs-mode-validation-identity.xlsx
+++ b/ig/nr-add-marital-status-binding/ValueSet-fr-core-vs-mode-validation-identity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-25T10:58:01+00:00</t>
+    <t>2024-01-29T09:41:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-marital-status-binding/ValueSet-fr-core-vs-mode-validation-identity.xlsx
+++ b/ig/nr-add-marital-status-binding/ValueSet-fr-core-vs-mode-validation-identity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:41:10+00:00</t>
+    <t>2024-01-29T10:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-marital-status-binding/ValueSet-fr-core-vs-mode-validation-identity.xlsx
+++ b/ig/nr-add-marital-status-binding/ValueSet-fr-core-vs-mode-validation-identity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:18:33+00:00</t>
+    <t>2024-01-29T10:24:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
